--- a/ttl_long/AdHoc_Net_11.xlsx
+++ b/ttl_long/AdHoc_Net_11.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>275</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>452</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>465</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>518</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>783</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>721</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>734</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>1121</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>1078</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>1057</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>1193</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>1133</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>1207</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1329</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>1455</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1354</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>1583</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1556</t>
         </is>
       </c>
     </row>
@@ -936,335 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>915</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1149</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1431</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1469</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1584</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>436</t>
+          <t>1509</t>
         </is>
       </c>
     </row>
@@ -1279,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,7 +989,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1334,7 +1011,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1356,7 +1033,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1378,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1422,7 +1099,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1444,7 +1121,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1461,12 +1138,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1527,12 +1204,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1549,12 +1226,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1571,12 +1248,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1593,7 +1270,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1615,12 +1292,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1637,12 +1314,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1659,12 +1336,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1681,7 +1358,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1703,12 +1380,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1725,12 +1402,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1747,12 +1424,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,12 +1446,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1796,7 +1473,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1813,12 +1490,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1840,7 +1517,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1862,7 +1539,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1879,12 +1556,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1906,7 +1583,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1928,7 +1605,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1945,12 +1622,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1967,12 +1644,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1989,12 +1666,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2011,12 +1688,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2033,12 +1710,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2055,12 +1732,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2077,12 +1754,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2099,12 +1776,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2121,12 +1798,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2143,12 +1820,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2165,12 +1842,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2187,12 +1864,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2209,12 +1886,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2231,12 +1908,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2253,12 +1930,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2275,12 +1952,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2297,12 +1974,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2319,12 +1996,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2341,12 +2018,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2363,12 +2040,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2385,12 +2062,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2407,12 +2084,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2429,12 +2106,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2451,12 +2128,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2473,12 +2150,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2495,12 +2172,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,12 +2194,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2539,12 +2216,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2561,12 +2238,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2583,12 +2260,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2605,12 +2282,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2627,12 +2304,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2649,12 +2326,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2671,12 +2348,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2693,12 +2370,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2715,12 +2392,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2737,12 +2414,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2759,12 +2436,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2781,12 +2458,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2803,12 +2480,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2825,12 +2502,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2847,12 +2524,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2861,1590 +2538,6 @@
         </is>
       </c>
       <c r="D72" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4483,7 +2576,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -4493,7 +2586,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -4519,7 +2612,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_11.xlsx
+++ b/ttl_long/AdHoc_Net_11.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>237</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>262</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>281</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>293</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>252</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>431</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>420</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>565</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>535</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>615</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>700</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>644</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>734</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>816</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>767</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>784</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>898</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>833</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1037</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>986</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1016</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1074</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1150</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,199 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>326</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1052</t>
         </is>
       </c>
     </row>
@@ -956,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1011,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1033,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1055,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1077,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1121,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1165,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1231,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1248,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1270,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1292,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1314,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1336,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1380,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1402,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1424,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1446,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1473,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1490,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1512,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1539,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1556,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1578,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1600,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1622,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1644,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1666,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1688,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1710,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1732,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1754,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1776,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1798,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1820,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1842,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1864,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1908,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1930,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1952,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1974,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1996,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2018,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2040,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2062,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2084,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2106,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2128,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2150,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2172,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2194,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2216,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2238,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2260,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2282,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2304,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2326,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2348,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2370,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2392,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2414,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2436,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2458,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2480,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2502,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2524,20 +2711,1032 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2576,7 +3775,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2586,7 +3785,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +3805,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_11.xlsx
+++ b/ttl_long/AdHoc_Net_11.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>339</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>219</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>436</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>401</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>575</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>545</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>530</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>631</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>547</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>647</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>812</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>274</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>687</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>770</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>843</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>796</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>875</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>953</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1017</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1096</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1148</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>955</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1322</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1208</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1243</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1368</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1358</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1385</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1551</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1577</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1501</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1673</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>177</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1605</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1413,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,7 +3415,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3437,7 +3437,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3649,94 +3649,6 @@
         </is>
       </c>
       <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3775,7 +3687,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
